--- a/data/nzd0086/nzd0086.xlsx
+++ b/data/nzd0086/nzd0086.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W292"/>
+  <dimension ref="A1:W293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22176,6 +22176,81 @@
       <c r="W292" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>264.04</v>
+      </c>
+      <c r="C293" t="n">
+        <v>240.28</v>
+      </c>
+      <c r="D293" t="n">
+        <v>226.08</v>
+      </c>
+      <c r="E293" t="n">
+        <v>242.98</v>
+      </c>
+      <c r="F293" t="n">
+        <v>252.64</v>
+      </c>
+      <c r="G293" t="n">
+        <v>260.43</v>
+      </c>
+      <c r="H293" t="n">
+        <v>268.92</v>
+      </c>
+      <c r="I293" t="n">
+        <v>266.95</v>
+      </c>
+      <c r="J293" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="K293" t="n">
+        <v>268.62</v>
+      </c>
+      <c r="L293" t="n">
+        <v>269.81</v>
+      </c>
+      <c r="M293" t="n">
+        <v>266.13</v>
+      </c>
+      <c r="N293" t="n">
+        <v>260.21</v>
+      </c>
+      <c r="O293" t="n">
+        <v>259.6</v>
+      </c>
+      <c r="P293" t="n">
+        <v>254.48</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>253.12</v>
+      </c>
+      <c r="R293" t="n">
+        <v>253.45</v>
+      </c>
+      <c r="S293" t="n">
+        <v>257.01</v>
+      </c>
+      <c r="T293" t="n">
+        <v>257.64</v>
+      </c>
+      <c r="U293" t="n">
+        <v>266.74</v>
+      </c>
+      <c r="V293" t="n">
+        <v>275.97</v>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -22190,7 +22265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B296"/>
+  <dimension ref="A1:B297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25153,6 +25228,16 @@
       </c>
       <c r="B296" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -25321,28 +25406,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5791107670323344</v>
+        <v>0.5416806468322821</v>
       </c>
       <c r="J2" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K2" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0505395946553534</v>
+        <v>0.04396580021688035</v>
       </c>
       <c r="M2" t="n">
-        <v>14.0029519231916</v>
+        <v>14.10286394327093</v>
       </c>
       <c r="N2" t="n">
-        <v>313.3159798939792</v>
+        <v>319.1060821057419</v>
       </c>
       <c r="O2" t="n">
-        <v>17.70073388009602</v>
+        <v>17.86354058146766</v>
       </c>
       <c r="P2" t="n">
-        <v>290.2372362972626</v>
+        <v>290.6600910985076</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25399,28 +25484,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>1.506454002746823</v>
+        <v>1.539765814596628</v>
       </c>
       <c r="J3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07946069096718211</v>
+        <v>0.08310118039203984</v>
       </c>
       <c r="M3" t="n">
-        <v>29.41031740314746</v>
+        <v>29.39433167962083</v>
       </c>
       <c r="N3" t="n">
-        <v>1249.126009377804</v>
+        <v>1249.907011734766</v>
       </c>
       <c r="O3" t="n">
-        <v>35.34297680413754</v>
+        <v>35.35402398221122</v>
       </c>
       <c r="P3" t="n">
-        <v>161.5869262421367</v>
+        <v>161.2029867507525</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25477,28 +25562,28 @@
         <v>0.0205</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.067311189241451</v>
+        <v>-1.061337386879545</v>
       </c>
       <c r="J4" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K4" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07211998577384615</v>
+        <v>0.07191118939328112</v>
       </c>
       <c r="M4" t="n">
-        <v>19.28024673879371</v>
+        <v>19.23714524989018</v>
       </c>
       <c r="N4" t="n">
-        <v>702.8836439728008</v>
+        <v>700.559332193863</v>
       </c>
       <c r="O4" t="n">
-        <v>26.51195285098404</v>
+        <v>26.46808138482771</v>
       </c>
       <c r="P4" t="n">
-        <v>247.0699198060713</v>
+        <v>247.0003803259212</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25555,28 +25640,28 @@
         <v>0.0258</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4098605106958924</v>
+        <v>-0.4115094218295272</v>
       </c>
       <c r="J5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0648899122473181</v>
+        <v>0.0658597183467835</v>
       </c>
       <c r="M5" t="n">
-        <v>8.521588425382081</v>
+        <v>8.500081432592456</v>
       </c>
       <c r="N5" t="n">
-        <v>130.2012755435788</v>
+        <v>129.7737078730904</v>
       </c>
       <c r="O5" t="n">
-        <v>11.41057735364775</v>
+        <v>11.3918263624886</v>
       </c>
       <c r="P5" t="n">
-        <v>256.2745850274503</v>
+        <v>256.2923135767018</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25633,28 +25718,28 @@
         <v>0.0318</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4230120847287869</v>
+        <v>-0.4257716769746984</v>
       </c>
       <c r="J6" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K6" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09058083048597754</v>
+        <v>0.0922800575222652</v>
       </c>
       <c r="M6" t="n">
-        <v>7.58809225110075</v>
+        <v>7.575743729371367</v>
       </c>
       <c r="N6" t="n">
-        <v>96.62530668630134</v>
+        <v>96.34573023211438</v>
       </c>
       <c r="O6" t="n">
-        <v>9.829817225477864</v>
+        <v>9.815586087041078</v>
       </c>
       <c r="P6" t="n">
-        <v>267.8517346141896</v>
+        <v>267.8814048408306</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25711,28 +25796,28 @@
         <v>0.039</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4051072586752561</v>
+        <v>-0.4112851838622164</v>
       </c>
       <c r="J7" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K7" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1026353882426336</v>
+        <v>0.105895930222184</v>
       </c>
       <c r="M7" t="n">
-        <v>7.082840902934774</v>
+        <v>7.080920518706733</v>
       </c>
       <c r="N7" t="n">
-        <v>77.17371183641241</v>
+        <v>77.16668569602045</v>
       </c>
       <c r="O7" t="n">
-        <v>8.78485696163645</v>
+        <v>8.784457051862708</v>
       </c>
       <c r="P7" t="n">
-        <v>279.9863611663591</v>
+        <v>280.0527841825636</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25789,28 +25874,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3462940463570596</v>
+        <v>-0.3526370993052216</v>
       </c>
       <c r="J8" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K8" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07500749367200155</v>
+        <v>0.07789286189564271</v>
       </c>
       <c r="M8" t="n">
-        <v>7.401284933758989</v>
+        <v>7.40485659005313</v>
       </c>
       <c r="N8" t="n">
-        <v>79.53918567704336</v>
+        <v>79.53799523000428</v>
       </c>
       <c r="O8" t="n">
-        <v>8.918474403004325</v>
+        <v>8.918407662245782</v>
       </c>
       <c r="P8" t="n">
-        <v>287.1368700722081</v>
+        <v>287.2050684876974</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25867,28 +25952,28 @@
         <v>0.0876</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2268031333611308</v>
+        <v>-0.233075761086135</v>
       </c>
       <c r="J9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373316423977833</v>
+        <v>0.03950411038161961</v>
       </c>
       <c r="M9" t="n">
-        <v>6.914816518678069</v>
+        <v>6.922088963280493</v>
       </c>
       <c r="N9" t="n">
-        <v>71.34363453561565</v>
+        <v>71.36452226431174</v>
       </c>
       <c r="O9" t="n">
-        <v>8.44651611823571</v>
+        <v>8.447752497813353</v>
       </c>
       <c r="P9" t="n">
-        <v>281.8676334019017</v>
+        <v>281.9350746285942</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25945,28 +26030,28 @@
         <v>0.0806</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1567831329385715</v>
+        <v>-0.165159841497651</v>
       </c>
       <c r="J10" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K10" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02204083926655476</v>
+        <v>0.02439820452097852</v>
       </c>
       <c r="M10" t="n">
-        <v>6.268993803798376</v>
+        <v>6.286260723935893</v>
       </c>
       <c r="N10" t="n">
-        <v>58.66091038720292</v>
+        <v>58.93300066068426</v>
       </c>
       <c r="O10" t="n">
-        <v>7.659041087969363</v>
+        <v>7.676783223504769</v>
       </c>
       <c r="P10" t="n">
-        <v>281.2140068275464</v>
+        <v>281.3040704381474</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26023,28 +26108,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000869110613306948</v>
+        <v>-0.008308204869873569</v>
       </c>
       <c r="J11" t="n">
+        <v>292</v>
+      </c>
+      <c r="K11" t="n">
         <v>291</v>
       </c>
-      <c r="K11" t="n">
-        <v>290</v>
-      </c>
       <c r="L11" t="n">
-        <v>7.33247473960752e-07</v>
+        <v>6.685041218612575e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>5.947239075068468</v>
+        <v>5.965562949012932</v>
       </c>
       <c r="N11" t="n">
-        <v>55.3755952073593</v>
+        <v>55.75318918653186</v>
       </c>
       <c r="O11" t="n">
-        <v>7.441478025725757</v>
+        <v>7.466805822206164</v>
       </c>
       <c r="P11" t="n">
-        <v>281.5305167707471</v>
+        <v>281.629355044284</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26101,28 +26186,28 @@
         <v>0.0562</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08810032019685285</v>
+        <v>-0.0985299789812995</v>
       </c>
       <c r="J12" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K12" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L12" t="n">
-        <v>0.009292181827192492</v>
+        <v>0.01149946428444548</v>
       </c>
       <c r="M12" t="n">
-        <v>5.440809103954679</v>
+        <v>5.475726952027069</v>
       </c>
       <c r="N12" t="n">
-        <v>44.50823726105301</v>
+        <v>45.08904083106432</v>
       </c>
       <c r="O12" t="n">
-        <v>6.671449412313115</v>
+        <v>6.71483736445376</v>
       </c>
       <c r="P12" t="n">
-        <v>286.8840263125584</v>
+        <v>286.9961625676087</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26179,28 +26264,28 @@
         <v>0.0536</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.003654015601963117</v>
+        <v>-0.01317020346534991</v>
       </c>
       <c r="J13" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K13" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L13" t="n">
-        <v>1.537291516862105e-05</v>
+        <v>0.0001986691523421236</v>
       </c>
       <c r="M13" t="n">
-        <v>5.426872935652275</v>
+        <v>5.450433313502566</v>
       </c>
       <c r="N13" t="n">
-        <v>46.71274811650642</v>
+        <v>47.16318833606509</v>
       </c>
       <c r="O13" t="n">
-        <v>6.834672495189979</v>
+        <v>6.867546019945195</v>
       </c>
       <c r="P13" t="n">
-        <v>279.654915814669</v>
+        <v>279.7572307313321</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26257,28 +26342,28 @@
         <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.009231242544386217</v>
+        <v>-0.01752578670828529</v>
       </c>
       <c r="J14" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K14" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001050900730578119</v>
+        <v>0.000377689972485995</v>
       </c>
       <c r="M14" t="n">
-        <v>5.074941387223175</v>
+        <v>5.100069855854485</v>
       </c>
       <c r="N14" t="n">
-        <v>43.60843662301344</v>
+        <v>43.92284328307093</v>
       </c>
       <c r="O14" t="n">
-        <v>6.603668421643643</v>
+        <v>6.627431122469016</v>
       </c>
       <c r="P14" t="n">
-        <v>272.1588146364558</v>
+        <v>272.2479948425499</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26335,28 +26420,28 @@
         <v>0.0704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04223115232028789</v>
+        <v>0.03699939530213987</v>
       </c>
       <c r="J15" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K15" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002290987659683497</v>
+        <v>0.001765718713581443</v>
       </c>
       <c r="M15" t="n">
-        <v>5.010745286679081</v>
+        <v>5.016065968813812</v>
       </c>
       <c r="N15" t="n">
-        <v>41.7738534483978</v>
+        <v>41.81529154905795</v>
       </c>
       <c r="O15" t="n">
-        <v>6.463269563340044</v>
+        <v>6.466474429629947</v>
       </c>
       <c r="P15" t="n">
-        <v>265.8465585239935</v>
+        <v>265.9028086517756</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26413,28 +26498,28 @@
         <v>0.059</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09746252056912023</v>
+        <v>0.09177025324186149</v>
       </c>
       <c r="J16" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K16" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01682102744419567</v>
+        <v>0.01495193732670852</v>
       </c>
       <c r="M16" t="n">
-        <v>4.275512524506762</v>
+        <v>4.28812022712444</v>
       </c>
       <c r="N16" t="n">
-        <v>29.86158598887324</v>
+        <v>29.97772903280448</v>
       </c>
       <c r="O16" t="n">
-        <v>5.464575554320138</v>
+        <v>5.475192145742876</v>
       </c>
       <c r="P16" t="n">
-        <v>259.9047140731166</v>
+        <v>259.9659154560205</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26491,28 +26576,28 @@
         <v>0.0731</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1213019704731647</v>
+        <v>0.1179753317779284</v>
       </c>
       <c r="J17" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K17" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02905385007612415</v>
+        <v>0.02766378247597023</v>
       </c>
       <c r="M17" t="n">
-        <v>4.127179055344201</v>
+        <v>4.127936101093061</v>
       </c>
       <c r="N17" t="n">
-        <v>26.4475041709193</v>
+        <v>26.43152569964037</v>
       </c>
       <c r="O17" t="n">
-        <v>5.142713697156327</v>
+        <v>5.141159956628502</v>
       </c>
       <c r="P17" t="n">
-        <v>254.5721332017921</v>
+        <v>254.6079001250347</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26569,28 +26654,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1118696079048301</v>
+        <v>0.1098037986114319</v>
       </c>
       <c r="J18" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K18" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02609298909019098</v>
+        <v>0.02533044381662974</v>
       </c>
       <c r="M18" t="n">
-        <v>3.969429083992396</v>
+        <v>3.96573067084872</v>
       </c>
       <c r="N18" t="n">
-        <v>25.12322693573208</v>
+        <v>25.06595451607484</v>
       </c>
       <c r="O18" t="n">
-        <v>5.012307546004344</v>
+        <v>5.00659110733789</v>
       </c>
       <c r="P18" t="n">
-        <v>253.3689255164584</v>
+        <v>253.3911364173706</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26647,28 +26732,28 @@
         <v>0.0756</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1123680807826851</v>
+        <v>0.1088728576429617</v>
       </c>
       <c r="J19" t="n">
+        <v>292</v>
+      </c>
+      <c r="K19" t="n">
         <v>291</v>
       </c>
-      <c r="K19" t="n">
-        <v>290</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02037308629734802</v>
+        <v>0.01925183246010675</v>
       </c>
       <c r="M19" t="n">
-        <v>4.502126674926357</v>
+        <v>4.505238495831006</v>
       </c>
       <c r="N19" t="n">
-        <v>32.75856979564676</v>
+        <v>32.72868763605139</v>
       </c>
       <c r="O19" t="n">
-        <v>5.723510268676624</v>
+        <v>5.720899198207515</v>
       </c>
       <c r="P19" t="n">
-        <v>258.9359185722986</v>
+        <v>258.9734589615725</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26725,28 +26810,28 @@
         <v>0.0958</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03496675368657481</v>
+        <v>0.03293442313451317</v>
       </c>
       <c r="J20" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K20" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002543966514449769</v>
+        <v>0.002273085423021071</v>
       </c>
       <c r="M20" t="n">
-        <v>3.975822652176479</v>
+        <v>3.971816911071625</v>
       </c>
       <c r="N20" t="n">
-        <v>25.78401408007855</v>
+        <v>25.72355387471066</v>
       </c>
       <c r="O20" t="n">
-        <v>5.077796183392806</v>
+        <v>5.071839298983225</v>
       </c>
       <c r="P20" t="n">
-        <v>259.5716770001657</v>
+        <v>259.5935279486811</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26803,28 +26888,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.169726382373856</v>
+        <v>0.1656416852923857</v>
       </c>
       <c r="J21" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K21" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0580250234713624</v>
+        <v>0.0556025109926781</v>
       </c>
       <c r="M21" t="n">
-        <v>3.797647974125897</v>
+        <v>3.807301650066267</v>
       </c>
       <c r="N21" t="n">
-        <v>25.15244918269658</v>
+        <v>25.17877611880634</v>
       </c>
       <c r="O21" t="n">
-        <v>5.015221748108112</v>
+        <v>5.017845764748688</v>
       </c>
       <c r="P21" t="n">
-        <v>267.9606451074983</v>
+        <v>268.0045624247564</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26881,28 +26966,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2761030354226626</v>
+        <v>0.2719444403832278</v>
       </c>
       <c r="J22" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K22" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08870080443007777</v>
+        <v>0.08668940682164716</v>
       </c>
       <c r="M22" t="n">
-        <v>5.122259876765049</v>
+        <v>5.127643868723239</v>
       </c>
       <c r="N22" t="n">
-        <v>42.12436050042217</v>
+        <v>42.09667058152267</v>
       </c>
       <c r="O22" t="n">
-        <v>6.490328227479884</v>
+        <v>6.488194708971261</v>
       </c>
       <c r="P22" t="n">
-        <v>274.4493845287145</v>
+        <v>274.49409637247</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26940,7 +27025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W292"/>
+  <dimension ref="A1:W293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60719,6 +60804,123 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>-35.513900989253116,174.47047550248027</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>-35.513892480576466,174.46953728694228</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>-35.51405243023557,174.46835991482132</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-35.514771948476366,174.46748397604938</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-35.51536617887497,174.4668565460598</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-35.515949442576286,174.4662173031047</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-35.51664898348202,174.46560014638203</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>-35.51735090248471,174.46508585881264</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-35.51798116525596,174.46462975360745</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-35.518633788789664,174.4642236612795</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-35.51932742125165,174.463763918155</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-35.52005203072416,174.46336806850007</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-35.52072060935332,174.4629847231038</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-35.521413532389744,174.4626528170425</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-35.522112733101096,174.46229154044119</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>-35.522818034700194,174.4619979766276</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>-35.52351840502805,174.46172601480743</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>-35.52431441404494,174.46146689720527</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>-35.52512903669491,174.46135239000938</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>-35.52586418351531,174.46134804360398</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>-35.52659944917939,174.4613456776654</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0086/nzd0086.xlsx
+++ b/data/nzd0086/nzd0086.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W293"/>
+  <dimension ref="A1:W295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22189,7 +22189,7 @@
         <v>264.04</v>
       </c>
       <c r="C293" t="n">
-        <v>240.28</v>
+        <v>194.76</v>
       </c>
       <c r="D293" t="n">
         <v>226.08</v>
@@ -22249,6 +22249,156 @@
         <v>275.97</v>
       </c>
       <c r="W293" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>269.03</v>
+      </c>
+      <c r="C294" t="n">
+        <v>188.33</v>
+      </c>
+      <c r="D294" t="n">
+        <v>227.84</v>
+      </c>
+      <c r="E294" t="n">
+        <v>239.96</v>
+      </c>
+      <c r="F294" t="n">
+        <v>247.83</v>
+      </c>
+      <c r="G294" t="n">
+        <v>255.96</v>
+      </c>
+      <c r="H294" t="n">
+        <v>264.87</v>
+      </c>
+      <c r="I294" t="n">
+        <v>264.9</v>
+      </c>
+      <c r="J294" t="n">
+        <v>263.09</v>
+      </c>
+      <c r="K294" t="n">
+        <v>267.25</v>
+      </c>
+      <c r="L294" t="n">
+        <v>266.96</v>
+      </c>
+      <c r="M294" t="n">
+        <v>261.93</v>
+      </c>
+      <c r="N294" t="n">
+        <v>258.29</v>
+      </c>
+      <c r="O294" t="n">
+        <v>256.33</v>
+      </c>
+      <c r="P294" t="n">
+        <v>252.69</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>250.59</v>
+      </c>
+      <c r="R294" t="n">
+        <v>250.98</v>
+      </c>
+      <c r="S294" t="n">
+        <v>252.66</v>
+      </c>
+      <c r="T294" t="n">
+        <v>255.96</v>
+      </c>
+      <c r="U294" t="n">
+        <v>264.43</v>
+      </c>
+      <c r="V294" t="n">
+        <v>273.02</v>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>269.03</v>
+      </c>
+      <c r="C295" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="D295" t="n">
+        <v>225.04</v>
+      </c>
+      <c r="E295" t="n">
+        <v>238.83</v>
+      </c>
+      <c r="F295" t="n">
+        <v>248.3</v>
+      </c>
+      <c r="G295" t="n">
+        <v>257.37</v>
+      </c>
+      <c r="H295" t="n">
+        <v>265.98</v>
+      </c>
+      <c r="I295" t="n">
+        <v>265.72</v>
+      </c>
+      <c r="J295" t="n">
+        <v>263.62</v>
+      </c>
+      <c r="K295" t="n">
+        <v>267.61</v>
+      </c>
+      <c r="L295" t="n">
+        <v>268.43</v>
+      </c>
+      <c r="M295" t="n">
+        <v>264.11</v>
+      </c>
+      <c r="N295" t="n">
+        <v>258.81</v>
+      </c>
+      <c r="O295" t="n">
+        <v>258.1</v>
+      </c>
+      <c r="P295" t="n">
+        <v>253.05</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>251.83</v>
+      </c>
+      <c r="R295" t="n">
+        <v>251.36</v>
+      </c>
+      <c r="S295" t="n">
+        <v>253.92</v>
+      </c>
+      <c r="T295" t="n">
+        <v>256.43</v>
+      </c>
+      <c r="U295" t="n">
+        <v>265.23</v>
+      </c>
+      <c r="V295" t="n">
+        <v>273.59</v>
+      </c>
+      <c r="W295" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22265,7 +22415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B297"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25238,6 +25388,26 @@
       </c>
       <c r="B297" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -25406,28 +25576,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5416806468322821</v>
+        <v>0.4780698443262079</v>
       </c>
       <c r="J2" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K2" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04396580021688035</v>
+        <v>0.03415093034013095</v>
       </c>
       <c r="M2" t="n">
-        <v>14.10286394327093</v>
+        <v>14.25205213858531</v>
       </c>
       <c r="N2" t="n">
-        <v>319.1060821057419</v>
+        <v>326.9213207595886</v>
       </c>
       <c r="O2" t="n">
-        <v>17.86354058146766</v>
+        <v>18.08096570318047</v>
       </c>
       <c r="P2" t="n">
-        <v>290.6600910985076</v>
+        <v>291.3807654419234</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25484,28 +25654,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>1.539765814596628</v>
+        <v>1.47297252650941</v>
       </c>
       <c r="J3" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K3" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08310118039203984</v>
+        <v>0.07812091128071752</v>
       </c>
       <c r="M3" t="n">
-        <v>29.39433167962083</v>
+        <v>29.26692889581504</v>
       </c>
       <c r="N3" t="n">
-        <v>1249.907011734766</v>
+        <v>1237.013554796811</v>
       </c>
       <c r="O3" t="n">
-        <v>35.35402398221122</v>
+        <v>35.17120348803564</v>
       </c>
       <c r="P3" t="n">
-        <v>161.2029867507525</v>
+        <v>161.9736863949179</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25562,28 +25732,28 @@
         <v>0.0205</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.061337386879545</v>
+        <v>-1.049038970592712</v>
       </c>
       <c r="J4" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K4" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07191118939328112</v>
+        <v>0.07142395046870131</v>
       </c>
       <c r="M4" t="n">
-        <v>19.23714524989018</v>
+        <v>19.15305031380749</v>
       </c>
       <c r="N4" t="n">
-        <v>700.559332193863</v>
+        <v>696.0078337303452</v>
       </c>
       <c r="O4" t="n">
-        <v>26.46808138482771</v>
+        <v>26.38196038451929</v>
       </c>
       <c r="P4" t="n">
-        <v>247.0003803259212</v>
+        <v>246.8568236177506</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25640,28 +25810,28 @@
         <v>0.0258</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4115094218295272</v>
+        <v>-0.4196727662286056</v>
       </c>
       <c r="J5" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K5" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0658597183467835</v>
+        <v>0.06921813467967419</v>
       </c>
       <c r="M5" t="n">
-        <v>8.500081432592456</v>
+        <v>8.480227174942254</v>
       </c>
       <c r="N5" t="n">
-        <v>129.7737078730904</v>
+        <v>129.1206776525911</v>
       </c>
       <c r="O5" t="n">
-        <v>11.3918263624886</v>
+        <v>11.36312798716054</v>
       </c>
       <c r="P5" t="n">
-        <v>256.2923135767018</v>
+        <v>256.3803555196849</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25718,28 +25888,28 @@
         <v>0.0318</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4257716769746984</v>
+        <v>-0.4374757807692262</v>
       </c>
       <c r="J6" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K6" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0922800575222652</v>
+        <v>0.09788728047274742</v>
       </c>
       <c r="M6" t="n">
-        <v>7.575743729371367</v>
+        <v>7.581922942385712</v>
       </c>
       <c r="N6" t="n">
-        <v>96.34573023211438</v>
+        <v>96.15874201443985</v>
       </c>
       <c r="O6" t="n">
-        <v>9.815586087041078</v>
+        <v>9.806056394618576</v>
       </c>
       <c r="P6" t="n">
-        <v>267.8814048408306</v>
+        <v>268.0076269956636</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25796,28 +25966,28 @@
         <v>0.039</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4112851838622164</v>
+        <v>-0.4285111768662521</v>
       </c>
       <c r="J7" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K7" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.105895930222184</v>
+        <v>0.1141879071173842</v>
       </c>
       <c r="M7" t="n">
-        <v>7.080920518706733</v>
+        <v>7.096156385959621</v>
       </c>
       <c r="N7" t="n">
-        <v>77.16668569602045</v>
+        <v>77.65903684709254</v>
       </c>
       <c r="O7" t="n">
-        <v>8.784457051862708</v>
+        <v>8.81243648754943</v>
       </c>
       <c r="P7" t="n">
-        <v>280.0527841825636</v>
+        <v>280.2385544528094</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25874,28 +26044,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3526370993052216</v>
+        <v>-0.3698190594180095</v>
       </c>
       <c r="J8" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K8" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07789286189564271</v>
+        <v>0.08525014394060559</v>
       </c>
       <c r="M8" t="n">
-        <v>7.40485659005313</v>
+        <v>7.432692715415158</v>
       </c>
       <c r="N8" t="n">
-        <v>79.53799523000428</v>
+        <v>80.00774097457905</v>
       </c>
       <c r="O8" t="n">
-        <v>8.918407662245782</v>
+        <v>8.944704633165873</v>
       </c>
       <c r="P8" t="n">
-        <v>287.2050684876974</v>
+        <v>287.3903648642514</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25952,28 +26122,28 @@
         <v>0.0876</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.233075761086135</v>
+        <v>-0.2475452116163408</v>
       </c>
       <c r="J9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03950411038161961</v>
+        <v>0.04458230894684989</v>
       </c>
       <c r="M9" t="n">
-        <v>6.922088963280493</v>
+        <v>6.946296612712125</v>
       </c>
       <c r="N9" t="n">
-        <v>71.36452226431174</v>
+        <v>71.59554205192615</v>
       </c>
       <c r="O9" t="n">
-        <v>8.447752497813353</v>
+        <v>8.461414896571739</v>
       </c>
       <c r="P9" t="n">
-        <v>281.9350746285942</v>
+        <v>282.0911187298514</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26030,28 +26200,28 @@
         <v>0.0806</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.165159841497651</v>
+        <v>-0.1840201774174849</v>
       </c>
       <c r="J10" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K10" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02439820452097852</v>
+        <v>0.02997354700821298</v>
       </c>
       <c r="M10" t="n">
-        <v>6.286260723935893</v>
+        <v>6.338380706198923</v>
       </c>
       <c r="N10" t="n">
-        <v>58.93300066068426</v>
+        <v>59.74788390159689</v>
       </c>
       <c r="O10" t="n">
-        <v>7.676783223504769</v>
+        <v>7.729675536631333</v>
       </c>
       <c r="P10" t="n">
-        <v>281.3040704381474</v>
+        <v>281.5074693377543</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26108,28 +26278,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.008308204869873569</v>
+        <v>-0.02783922779505037</v>
       </c>
       <c r="J11" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K11" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L11" t="n">
-        <v>6.685041218612575e-05</v>
+        <v>0.0007445126487510834</v>
       </c>
       <c r="M11" t="n">
-        <v>5.965562949012932</v>
+        <v>6.007449341408223</v>
       </c>
       <c r="N11" t="n">
-        <v>55.75318918653186</v>
+        <v>56.67643139582673</v>
       </c>
       <c r="O11" t="n">
-        <v>7.466805822206164</v>
+        <v>7.528375083364718</v>
       </c>
       <c r="P11" t="n">
-        <v>281.629355044284</v>
+        <v>281.8403453560683</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26186,28 +26356,28 @@
         <v>0.0562</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0985299789812995</v>
+        <v>-0.121770071750801</v>
       </c>
       <c r="J12" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K12" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01149946428444548</v>
+        <v>0.0170406028218939</v>
       </c>
       <c r="M12" t="n">
-        <v>5.475726952027069</v>
+        <v>5.55725602787428</v>
       </c>
       <c r="N12" t="n">
-        <v>45.08904083106432</v>
+        <v>46.63134570142612</v>
       </c>
       <c r="O12" t="n">
-        <v>6.71483736445376</v>
+        <v>6.828714791337102</v>
       </c>
       <c r="P12" t="n">
-        <v>286.9961625676087</v>
+        <v>287.2467921672029</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26264,28 +26434,28 @@
         <v>0.0536</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.01317020346534991</v>
+        <v>-0.03602716165061672</v>
       </c>
       <c r="J13" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K13" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0001986691523421236</v>
+        <v>0.001452852095284785</v>
       </c>
       <c r="M13" t="n">
-        <v>5.450433313502566</v>
+        <v>5.517716351505869</v>
       </c>
       <c r="N13" t="n">
-        <v>47.16318833606509</v>
+        <v>48.63550927534927</v>
       </c>
       <c r="O13" t="n">
-        <v>6.867546019945195</v>
+        <v>6.973916351330096</v>
       </c>
       <c r="P13" t="n">
-        <v>279.7572307313321</v>
+        <v>280.0037260295039</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26342,28 +26512,28 @@
         <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01752578670828529</v>
+        <v>-0.03597625773587738</v>
       </c>
       <c r="J14" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K14" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000377689972485995</v>
+        <v>0.001573030200821335</v>
       </c>
       <c r="M14" t="n">
-        <v>5.100069855854485</v>
+        <v>5.159892004122302</v>
       </c>
       <c r="N14" t="n">
-        <v>43.92284328307093</v>
+        <v>44.78756121274191</v>
       </c>
       <c r="O14" t="n">
-        <v>6.627431122469016</v>
+        <v>6.692350948115461</v>
       </c>
       <c r="P14" t="n">
-        <v>272.2479948425499</v>
+        <v>272.4469735760178</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26420,28 +26590,28 @@
         <v>0.0704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03699939530213987</v>
+        <v>0.02349455795267433</v>
       </c>
       <c r="J15" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K15" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001765718713581443</v>
+        <v>0.0007133072362467408</v>
       </c>
       <c r="M15" t="n">
-        <v>5.016065968813812</v>
+        <v>5.039722150206424</v>
       </c>
       <c r="N15" t="n">
-        <v>41.81529154905795</v>
+        <v>42.15938147893985</v>
       </c>
       <c r="O15" t="n">
-        <v>6.466474429629947</v>
+        <v>6.493025602824915</v>
       </c>
       <c r="P15" t="n">
-        <v>265.9028086517756</v>
+        <v>266.0484466572374</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26498,28 +26668,28 @@
         <v>0.059</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09177025324186149</v>
+        <v>0.07843679061254315</v>
       </c>
       <c r="J16" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K16" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01495193732670852</v>
+        <v>0.0109196698640921</v>
       </c>
       <c r="M16" t="n">
-        <v>4.28812022712444</v>
+        <v>4.322252868108714</v>
       </c>
       <c r="N16" t="n">
-        <v>29.97772903280448</v>
+        <v>30.38140732891737</v>
       </c>
       <c r="O16" t="n">
-        <v>5.475192145742876</v>
+        <v>5.511933175294977</v>
       </c>
       <c r="P16" t="n">
-        <v>259.9659154560205</v>
+        <v>260.1097099808038</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26576,28 +26746,28 @@
         <v>0.0731</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1179753317779284</v>
+        <v>0.1088139336997739</v>
       </c>
       <c r="J17" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K17" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02766378247597023</v>
+        <v>0.0237443036787004</v>
       </c>
       <c r="M17" t="n">
-        <v>4.127936101093061</v>
+        <v>4.141226228305334</v>
       </c>
       <c r="N17" t="n">
-        <v>26.43152569964037</v>
+        <v>26.5411272455291</v>
       </c>
       <c r="O17" t="n">
-        <v>5.141159956628502</v>
+        <v>5.151808153020558</v>
       </c>
       <c r="P17" t="n">
-        <v>254.6079001250347</v>
+        <v>254.7066977696127</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26654,28 +26824,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1098037986114319</v>
+        <v>0.1025908218135808</v>
       </c>
       <c r="J18" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K18" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02533044381662974</v>
+        <v>0.02237291391459906</v>
       </c>
       <c r="M18" t="n">
-        <v>3.96573067084872</v>
+        <v>3.972818535153294</v>
       </c>
       <c r="N18" t="n">
-        <v>25.06595451607484</v>
+        <v>25.07343824736495</v>
       </c>
       <c r="O18" t="n">
-        <v>5.00659110733789</v>
+        <v>5.007338439467113</v>
       </c>
       <c r="P18" t="n">
-        <v>253.3911364173706</v>
+        <v>253.4689240388859</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26732,28 +26902,28 @@
         <v>0.0756</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1088728576429617</v>
+        <v>0.0968689540443604</v>
       </c>
       <c r="J19" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K19" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01925183246010675</v>
+        <v>0.01531160549833444</v>
       </c>
       <c r="M19" t="n">
-        <v>4.505238495831006</v>
+        <v>4.538149472357418</v>
       </c>
       <c r="N19" t="n">
-        <v>32.72868763605139</v>
+        <v>33.0023894239314</v>
       </c>
       <c r="O19" t="n">
-        <v>5.720899198207515</v>
+        <v>5.744770615432038</v>
       </c>
       <c r="P19" t="n">
-        <v>258.9734589615725</v>
+        <v>259.1027792040929</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26810,28 +26980,28 @@
         <v>0.0958</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03293442313451317</v>
+        <v>0.02695988104979633</v>
       </c>
       <c r="J20" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K20" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002273085423021071</v>
+        <v>0.001541243509539325</v>
       </c>
       <c r="M20" t="n">
-        <v>3.971816911071625</v>
+        <v>3.972661788355127</v>
       </c>
       <c r="N20" t="n">
-        <v>25.72355387471066</v>
+        <v>25.67089514382429</v>
       </c>
       <c r="O20" t="n">
-        <v>5.071839298983225</v>
+        <v>5.066645354060642</v>
       </c>
       <c r="P20" t="n">
-        <v>259.5935279486811</v>
+        <v>259.6579592853748</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26888,28 +27058,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1656416852923857</v>
+        <v>0.1550091389109616</v>
       </c>
       <c r="J21" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K21" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0556025109926781</v>
+        <v>0.04905369494164746</v>
       </c>
       <c r="M21" t="n">
-        <v>3.807301650066267</v>
+        <v>3.840014576681863</v>
       </c>
       <c r="N21" t="n">
-        <v>25.17877611880634</v>
+        <v>25.39481637072082</v>
       </c>
       <c r="O21" t="n">
-        <v>5.017845764748688</v>
+        <v>5.039326975968202</v>
       </c>
       <c r="P21" t="n">
-        <v>268.0045624247564</v>
+        <v>268.1192272777076</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26966,28 +27136,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2719444403832278</v>
+        <v>0.2600991841189873</v>
       </c>
       <c r="J22" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K22" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08668940682164716</v>
+        <v>0.08021752191496678</v>
       </c>
       <c r="M22" t="n">
-        <v>5.127643868723239</v>
+        <v>5.157200070546611</v>
       </c>
       <c r="N22" t="n">
-        <v>42.09667058152267</v>
+        <v>42.29023224409377</v>
       </c>
       <c r="O22" t="n">
-        <v>6.488194708971261</v>
+        <v>6.503094051610646</v>
       </c>
       <c r="P22" t="n">
-        <v>274.49409637247</v>
+        <v>274.6218405220692</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -27025,7 +27195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W293"/>
+  <dimension ref="A1:W295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60817,7 +60987,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-35.513892480576466,174.46953728694228</t>
+          <t>-35.51349846381699,174.4693971006529</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -60916,6 +61086,240 @@
         </is>
       </c>
       <c r="W293" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>-35.513944182108396,174.4704908704276</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>-35.513442806335156,174.46937729853124</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>-35.5140665384948,174.46836879232472</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>-35.514751416568856,174.4674621100879</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>-35.51533478993129,174.4668199574107</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-35.51592175620097,174.46618149269838</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-35.51662830358403,174.46556334509063</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-35.51734203407956,174.46506602796129</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>-35.51797203723899,174.464609342211</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-35.51862786204221,174.46421040829014</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-35.51931665523878,174.46373538497514</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-35.520038717803054,174.463324714317</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-35.52071460304913,174.46296486758155</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-35.52140367608105,174.4626188348986</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>-35.52210775254795,174.46227276614002</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>-35.52281129237759,174.46197132541016</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>-35.523511896359224,174.4616999676584</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>-35.52430663378519,174.46141988277157</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>-35.52512742893986,174.46133396892202</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>-35.525861979193664,174.46132271355083</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>-35.52659664223583,174.46131332841378</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>-35.513944182108396,174.4704908704276</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>-35.51340099830155,174.4693624238614</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>-35.51404409353658,174.46835466902536</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-35.514743734099035,174.46745392845622</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>-35.51533785704274,174.46682353259968</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>-35.515930489488355,174.4661927885957</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-35.51663397140908,174.46557343136865</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>-35.51734558144202,174.4650739603013</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-35.51797433005875,174.46461446924377</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-35.51862941943585,174.4642138908273</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-35.51932220823576,174.46375010208806</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-35.52004562784505,174.46334721720075</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>-35.52071622975685,174.46297024511853</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-35.521409011148435,174.4626372289021</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>-35.52210875422369,174.46227654197693</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>-35.5228145969159,174.46198438766638</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>-35.523512897693266,174.46170397491184</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>-35.52430888737958,174.4614335007446</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>-35.52512787872877,174.46133912244042</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>-35.5258627425957,174.46133148586347</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>-35.52659718459508,174.46131957894698</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
